--- a/xlsx/tests/calc_tests/DMIN_DMAX_DAVERAGE_DSUM.xlsx
+++ b/xlsx/tests/calc_tests/DMIN_DMAX_DAVERAGE_DSUM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elsam\Documents\IronCalc stuff\my_calc_tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DD0324-CEB7-4240-9E67-1F4DEE875CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF13CDB9-1A51-462C-AB56-1F36CBDBF2F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DMIN_DMAX_DAVERAGE_DSUM" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="112">
   <si>
     <t>Region</t>
   </si>
@@ -363,9 +363,6 @@
   </si>
   <si>
     <t>Field as decimal number (6.0000001)</t>
-  </si>
-  <si>
-    <t>Field as decimal number (6.9999999)</t>
   </si>
   <si>
     <t>Criteria with empty cells</t>
@@ -422,7 +419,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -438,6 +435,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -572,7 +575,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -622,6 +625,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -840,7 +846,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1009"/>
+  <dimension ref="A1:Z1008"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="6" width="12.59765625" style="4"/>
@@ -1772,7 +1778,7 @@
         <v>12</v>
       </c>
       <c r="P25" s="24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.45">
@@ -2709,10 +2715,7 @@
         <f>DAVERAGE($A$1:$G$11,$E$1:$F$1,$A$14:$A$15)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E64" s="21" t="e">
-        <f>DSUM($A$1:$G$11,$E$1:$F$1,$A$14:$A$15)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="E64" s="25"/>
       <c r="F64" s="22" t="s">
         <v>106</v>
       </c>
@@ -2773,20 +2776,20 @@
         <v>1</v>
       </c>
       <c r="B67" s="21">
-        <f>DMIN($A$1:$G$11,6.9999999,$A$14:$A$15)</f>
-        <v>45306</v>
+        <f>DMIN($A$1:$G$11,$F$1,$A$14:$A$17)</f>
+        <v>6000</v>
       </c>
       <c r="C67" s="21">
-        <f>DMAX($A$1:$G$11,6.9999999,$A$14:$A$15)</f>
-        <v>45571</v>
+        <f>DMAX($A$1:$G$11,$F$1,$A$14:$A$17)</f>
+        <v>38000</v>
       </c>
       <c r="D67" s="21">
-        <f>DAVERAGE($A$1:$G$11,6.9999999,$A$14:$A$15)</f>
-        <v>45437.5</v>
+        <f>DAVERAGE($A$1:$G$11,$F$1,$A$14:$A$17)</f>
+        <v>18540</v>
       </c>
       <c r="E67" s="21">
-        <f>DSUM($A$1:$G$11,6.9999999,$A$14:$A$15)</f>
-        <v>181750</v>
+        <f>DSUM($A$1:$G$11,$F$1,$A$14:$A$17)</f>
+        <v>185400</v>
       </c>
       <c r="F67" s="22" t="s">
         <v>109</v>
@@ -2795,23 +2798,23 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" s="22">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="B68" s="21">
-        <f>DMIN($A$1:$G$11,$F$1,$A$14:$A$17)</f>
+        <f>DMIN($A$1:$G$11,$F$1,P24:P25)</f>
         <v>6000</v>
       </c>
       <c r="C68" s="21">
-        <f>DMAX($A$1:$G$11,$F$1,$A$14:$A$17)</f>
+        <f>DMAX($A$1:$G$11,$F$1,P24:P25)</f>
         <v>38000</v>
       </c>
       <c r="D68" s="21">
-        <f>DAVERAGE($A$1:$G$11,$F$1,$A$14:$A$17)</f>
-        <v>18540</v>
+        <f>DAVERAGE($A$1:$G$11,$F$1,P24:P25)</f>
+        <v>21466.666666666668</v>
       </c>
       <c r="E68" s="21">
-        <f>DSUM($A$1:$G$11,$F$1,$A$14:$A$17)</f>
-        <v>185400</v>
+        <f>DSUM($A$1:$G$11,$F$1,P24:P25)</f>
+        <v>128800</v>
       </c>
       <c r="F68" s="22" t="s">
         <v>110</v>
@@ -2819,28 +2822,6 @@
       <c r="J68" s="9"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A69" s="22">
-        <v>36</v>
-      </c>
-      <c r="B69" s="21">
-        <f>DMIN($A$1:$G$11,$F$1,P24:P25)</f>
-        <v>6000</v>
-      </c>
-      <c r="C69" s="21">
-        <f>DMAX($A$1:$G$11,$F$1,P24:P25)</f>
-        <v>38000</v>
-      </c>
-      <c r="D69" s="21">
-        <f>DAVERAGE($A$1:$G$11,$F$1,P24:P25)</f>
-        <v>21466.666666666668</v>
-      </c>
-      <c r="E69" s="21">
-        <f>DSUM($A$1:$G$11,$F$1,P24:P25)</f>
-        <v>128800</v>
-      </c>
-      <c r="F69" s="22" t="s">
-        <v>111</v>
-      </c>
       <c r="J69" s="9"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
@@ -5659,9 +5640,6 @@
     </row>
     <row r="1008" spans="10:10" x14ac:dyDescent="0.45">
       <c r="J1008" s="9"/>
-    </row>
-    <row r="1009" spans="10:10" x14ac:dyDescent="0.45">
-      <c r="J1009" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
